--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -9,9 +9,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEM Kontrol Listesi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEM Kontrol Listesi'!$A$1:$N$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEM Kontrol Listesi'!$A$1:$U$350</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcMode="manual" fullCalcOnLoad="1" calcCompleted="0" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N350"/>
+  <dimension ref="A1:R350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,19 @@
           <t>2:41.06</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Unsal Firikci Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Adana</t>
+        </is>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" ht="15.95" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -692,6 +705,19 @@
           <t>2:49.45</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ageb Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Adana</t>
+        </is>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="15.95" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -762,6 +788,19 @@
           <t>02:38.79</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Adana Gençlik Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Adana</t>
+        </is>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="15.95" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -832,6 +871,19 @@
           <t>2:35.19</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Unsal Firikci Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Adana</t>
+        </is>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="15.95" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -849,7 +901,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Ahmet Tuna ATCI</t>
+          <t>Ahmet Tuna Atcı</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -901,6 +953,19 @@
         <is>
           <t>1:04.93</t>
         </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="15.95" customHeight="1">
@@ -972,6 +1037,12 @@
           <t>58.03</t>
         </is>
       </c>
+      <c r="Q7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R7" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="8" ht="15.95" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1042,6 +1113,19 @@
           <t>2:48.65</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Baskent Cankaya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="15.95" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -1112,6 +1196,19 @@
           <t>2:50.06</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="15.95" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1182,6 +1279,12 @@
           <t>2:16.19</t>
         </is>
       </c>
+      <c r="Q10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R10" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="11" ht="15.95" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -1252,6 +1355,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Baskent Cankaya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="15.95" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1322,6 +1438,19 @@
           <t>6:10.89</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Baskent Cankaya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" ht="15.95" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -1392,6 +1521,19 @@
           <t>6:12.90</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fatih Karakurt Alpha Academy Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="15.95" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1462,6 +1604,19 @@
           <t>2:36.45</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" ht="15.95" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -1532,6 +1687,12 @@
           <t>26.88</t>
         </is>
       </c>
+      <c r="Q15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R15" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="16" ht="15.95" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1602,6 +1763,19 @@
           <t>2:28.31</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" ht="15.95" customHeight="1">
       <c r="A17" s="4" t="n">
@@ -1672,6 +1846,19 @@
           <t>2:36.43</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gordion Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="15.95" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1742,6 +1929,19 @@
           <t>2:24.22</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="15.95" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -1812,6 +2012,19 @@
           <t>2:14.03</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" ht="15.95" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1878,6 +2091,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="15.95" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -1948,6 +2174,12 @@
           <t>32.65</t>
         </is>
       </c>
+      <c r="Q21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R21" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -2018,6 +2250,19 @@
           <t>2:51.77</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -2088,6 +2333,19 @@
           <t>30.41</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" ht="15.95" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -2158,6 +2416,19 @@
           <t>5:13.69</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" ht="15.95" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -2228,6 +2499,19 @@
           <t>2:44.26</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Baskent Cankaya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="15.95" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -2298,6 +2582,19 @@
           <t>1:11.85</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" ht="15.95" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -2368,6 +2665,19 @@
           <t>20:22.86</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" ht="15.95" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -2438,6 +2748,19 @@
           <t>1:12.57</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" ht="15.95" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -2508,6 +2831,19 @@
           <t>2:40.39</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" ht="15.95" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -2578,6 +2914,19 @@
           <t>1:03.93</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="15.95" customHeight="1">
       <c r="A31" s="4" t="n">
@@ -2648,6 +2997,19 @@
           <t>2:33.56</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" ht="15.95" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -2718,6 +3080,12 @@
           <t>1:04.94</t>
         </is>
       </c>
+      <c r="Q32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R32" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -2788,6 +3156,12 @@
           <t>4:58.40</t>
         </is>
       </c>
+      <c r="Q33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R33" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -2858,6 +3232,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="4" t="n">
@@ -2928,6 +3315,19 @@
           <t>16:08.69</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -2998,6 +3398,19 @@
           <t>2:14.64</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ferdi</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -3015,10 +3428,14 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Ömer Selman KARAKÖS1E4</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
+          <t>Ömer Selman KARAKÖSE</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>69913227489</t>
@@ -3063,6 +3480,14 @@
         <is>
           <t>2:58.58</t>
         </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R37" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="38" ht="15.95" customHeight="1">
@@ -3134,6 +3559,19 @@
           <t>2:50.08</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ferdi</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="4" t="n">
@@ -3204,6 +3642,19 @@
           <t>2:43.73</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Aykon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -3274,6 +3725,19 @@
           <t>2:36.79</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="4" t="n">
@@ -3291,7 +3755,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>B. ALTUNZİNCİR</t>
+          <t>Başak İrem ALTUNZİNCİR</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3343,6 +3807,14 @@
         <is>
           <t>2:57.02</t>
         </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R41" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="42" ht="15.95" customHeight="1">
@@ -3414,6 +3886,19 @@
           <t>2:29.48</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" ht="15.95" customHeight="1">
       <c r="A43" s="4" t="n">
@@ -3484,6 +3969,19 @@
           <t>2:39.85</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" ht="15.95" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -3554,6 +4052,19 @@
           <t>2:50.91</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" ht="15.95" customHeight="1">
       <c r="A45" s="4" t="n">
@@ -3624,6 +4135,12 @@
           <t>2:29.83</t>
         </is>
       </c>
+      <c r="Q45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R45" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="46" ht="15.95" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -3694,6 +4211,19 @@
           <t>2:42.39</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vamos Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" ht="15.95" customHeight="1">
       <c r="A47" s="4" t="n">
@@ -3764,6 +4294,19 @@
           <t>2:58.25</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" ht="15.95" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -3834,6 +4377,19 @@
           <t>2:49.03</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Baskent Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" ht="15.95" customHeight="1">
       <c r="A49" s="4" t="n">
@@ -3904,6 +4460,19 @@
           <t>2:39.72</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" ht="15.95" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -3974,6 +4543,12 @@
           <t>17:41.05</t>
         </is>
       </c>
+      <c r="Q50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R50" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="51" ht="15.95" customHeight="1">
       <c r="A51" s="4" t="n">
@@ -4044,6 +4619,19 @@
           <t>2:43.72</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ted Ankara Kolejliler Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" ht="15.95" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -4114,6 +4702,19 @@
           <t>2:42.93</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ferdi</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" ht="15.95" customHeight="1">
       <c r="A53" s="4" t="n">
@@ -4184,6 +4785,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Baskent Cankaya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" ht="15.95" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -4254,6 +4868,19 @@
           <t>2:46.92</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" ht="15.95" customHeight="1">
       <c r="A55" s="4" t="n">
@@ -4324,6 +4951,19 @@
           <t>20:14.97</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Orka Swim Team Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" ht="15.95" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -4394,6 +5034,19 @@
           <t>2:41.16</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nesibe Aydın Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" ht="15.95" customHeight="1">
       <c r="A57" s="4" t="n">
@@ -4464,6 +5117,19 @@
           <t>2:43.83</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kulac Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" ht="15.95" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -4534,6 +5200,19 @@
           <t>15:56.41</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Antalya Bahcesehir Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" ht="15.95" customHeight="1">
       <c r="A59" s="4" t="n">
@@ -4604,6 +5283,19 @@
           <t>2:22.89</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" ht="15.95" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -4674,6 +5366,17 @@
           <t>2:31.62</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" ht="15.95" customHeight="1">
       <c r="A61" s="4" t="n">
@@ -4744,6 +5447,19 @@
           <t>2:44.66</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" ht="15.95" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -4814,6 +5530,19 @@
           <t>18:29.55</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" ht="15.95" customHeight="1">
       <c r="A63" s="4" t="n">
@@ -4884,6 +5613,19 @@
           <t>5:45.24</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Manavgat Barlas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" ht="15.95" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -4954,6 +5696,19 @@
           <t>2:48.60</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" ht="15.95" customHeight="1">
       <c r="A65" s="4" t="n">
@@ -5024,6 +5779,19 @@
           <t>2:37.40</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" ht="15.95" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -5094,6 +5862,19 @@
           <t>19:14.74</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" ht="15.95" customHeight="1">
       <c r="A67" s="4" t="n">
@@ -5164,6 +5945,19 @@
           <t>17:24.82</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" ht="15.95" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -5234,6 +6028,19 @@
           <t>5:08.01</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Muratpaşa Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" ht="15.95" customHeight="1">
       <c r="A69" s="4" t="n">
@@ -5304,6 +6111,19 @@
           <t>5:36.03</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Manavgat Barlas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" ht="15.95" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -5374,6 +6194,19 @@
           <t>5:32.02</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Alanya Gençlik ve Spor İlçe Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" ht="15.95" customHeight="1">
       <c r="A71" s="4" t="n">
@@ -5444,6 +6277,17 @@
           <t>2:50.84</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Antalya Faroz Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="72" ht="15.95" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -5514,6 +6358,19 @@
           <t>2:32.18</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Antalyaspor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" ht="15.95" customHeight="1">
       <c r="A73" s="4" t="n">
@@ -5584,6 +6441,19 @@
           <t>5:57.42</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Manavgat Barlas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" ht="15.95" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -5654,6 +6524,19 @@
           <t>2:51.29</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" ht="15.95" customHeight="1">
       <c r="A75" s="4" t="n">
@@ -5724,6 +6607,19 @@
           <t>5:47.86</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" ht="15.95" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -5794,6 +6690,19 @@
           <t>2:45.34</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Toroslar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" ht="15.95" customHeight="1">
       <c r="A77" s="4" t="n">
@@ -5864,6 +6773,19 @@
           <t>2:33.36</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kulac Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" ht="15.95" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -5934,6 +6856,19 @@
           <t>2:44.85</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Muratpaşa Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" ht="15.95" customHeight="1">
       <c r="A79" s="4" t="n">
@@ -6004,6 +6939,19 @@
           <t>2:59.61</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bolu Gençlik ve Spor İl Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="R79" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" ht="15.95" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -6074,6 +7022,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bolu Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="R80" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" ht="15.95" customHeight="1">
       <c r="A81" s="4" t="n">
@@ -6144,6 +7105,12 @@
           <t>25.73</t>
         </is>
       </c>
+      <c r="Q81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R81" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="82" ht="15.95" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -6214,6 +7181,19 @@
           <t>1:12.75</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bosch Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" ht="15.95" customHeight="1">
       <c r="A83" s="4" t="n">
@@ -6284,6 +7264,12 @@
           <t>58.37</t>
         </is>
       </c>
+      <c r="Q83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R83" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="84" ht="15.95" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -6354,6 +7340,19 @@
           <t>2:48.39</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" ht="15.95" customHeight="1">
       <c r="A85" s="4" t="n">
@@ -6424,6 +7423,19 @@
           <t>18:58.44</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" ht="15.95" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -6494,6 +7506,19 @@
           <t>2:46.54</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" ht="15.95" customHeight="1">
       <c r="A87" s="4" t="n">
@@ -6564,6 +7589,19 @@
           <t>2:30.92</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bursa Büyükşehir Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" ht="15.95" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -6630,6 +7668,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bursa Büyükşehir Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" ht="15.95" customHeight="1">
       <c r="A89" s="4" t="n">
@@ -6700,6 +7751,19 @@
           <t>2:49.59</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R89" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" ht="15.95" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -6770,6 +7834,19 @@
           <t>2:13.32</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" ht="15.95" customHeight="1">
       <c r="A91" s="4" t="n">
@@ -6840,6 +7917,12 @@
           <t>56.43</t>
         </is>
       </c>
+      <c r="Q91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R91" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="92" ht="15.95" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -6910,6 +7993,12 @@
           <t>8:29.08</t>
         </is>
       </c>
+      <c r="Q92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R92" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="93" ht="15.95" customHeight="1">
       <c r="A93" s="4" t="n">
@@ -6980,6 +8069,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" ht="15.95" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -7050,6 +8152,19 @@
           <t>5:30.27</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" ht="15.95" customHeight="1">
       <c r="A95" s="4" t="n">
@@ -7120,6 +8235,19 @@
           <t>39.35</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bursa Büyükşehir Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" ht="15.95" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -7190,6 +8318,19 @@
           <t>17:20.50</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" ht="15.95" customHeight="1">
       <c r="A97" s="4" t="n">
@@ -7260,6 +8401,19 @@
           <t>2:22.87</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" ht="15.95" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -7330,6 +8484,12 @@
           <t>2:19.42</t>
         </is>
       </c>
+      <c r="Q98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R98" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="99" ht="15.95" customHeight="1">
       <c r="A99" s="4" t="n">
@@ -7400,6 +8560,19 @@
           <t>2:47.93</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" ht="15.95" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -7470,6 +8643,19 @@
           <t>2:43.86</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bursa Büyükşehir Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" ht="15.95" customHeight="1">
       <c r="A101" s="4" t="n">
@@ -7540,6 +8726,12 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" ht="15.95" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -7610,6 +8802,19 @@
           <t>1:03.83</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103" ht="15.95" customHeight="1">
       <c r="A103" s="4" t="n">
@@ -7680,6 +8885,19 @@
           <t>2:45.84</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104" ht="15.95" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -7750,6 +8968,19 @@
           <t>5:25.58</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Turkıye</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105" ht="15.95" customHeight="1">
       <c r="A105" s="4" t="n">
@@ -7820,6 +9051,19 @@
           <t>1:20.41</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106" ht="15.95" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -7890,6 +9134,12 @@
           <t>2:22.48</t>
         </is>
       </c>
+      <c r="Q106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R106" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="107" ht="15.95" customHeight="1">
       <c r="A107" s="4" t="n">
@@ -7960,6 +9210,19 @@
           <t>5:34.49</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" ht="15.95" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -8030,6 +9293,19 @@
           <t>5:29.53</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109" ht="15.95" customHeight="1">
       <c r="A109" s="4" t="n">
@@ -8100,6 +9376,12 @@
           <t>33.53</t>
         </is>
       </c>
+      <c r="Q109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R109" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="110" ht="15.95" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -8166,6 +9448,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Bosch Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111" ht="15.95" customHeight="1">
       <c r="A111" s="4" t="n">
@@ -8236,6 +9531,19 @@
           <t>13:02.44</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" ht="15.95" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -8306,6 +9614,19 @@
           <t>2:30.54</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Bosch Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R112" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" ht="15.95" customHeight="1">
       <c r="A113" s="4" t="n">
@@ -8372,6 +9693,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Bosch Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R113" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="114" ht="15.95" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -8442,6 +9776,19 @@
           <t>2:25.83</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R114" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" ht="15.95" customHeight="1">
       <c r="A115" s="4" t="n">
@@ -8512,6 +9859,14 @@
           <t>9:39.64</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" ht="15.95" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -8582,6 +9937,19 @@
           <t>1:16.45</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Bursa Osmangazi Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" ht="15.95" customHeight="1">
       <c r="A117" s="4" t="n">
@@ -8652,6 +10020,19 @@
           <t>5:26.12</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ortakçı Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R117" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="15.95" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -8722,6 +10103,19 @@
           <t>2:42.47</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R118" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" ht="15.95" customHeight="1">
       <c r="A119" s="4" t="n">
@@ -8792,6 +10186,19 @@
           <t>2:54.49</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R119" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" ht="15.95" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -8862,6 +10269,19 @@
           <t>5:42.83</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Uludağ Oksijen Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="R120" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="15.95" customHeight="1">
       <c r="A121" s="4" t="n">
@@ -8932,6 +10352,19 @@
           <t>2:31.74</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Poseidon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="R121" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="15.95" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -9002,6 +10435,19 @@
           <t>2:27.67</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Poseidon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="R122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123" ht="15.95" customHeight="1">
       <c r="A123" s="4" t="n">
@@ -9072,6 +10518,19 @@
           <t>5:17.70</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Poseidon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="R123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124" ht="15.95" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -9142,6 +10601,19 @@
           <t>28.00</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Poseidon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="R124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" ht="15.95" customHeight="1">
       <c r="A125" s="4" t="n">
@@ -9212,6 +10684,12 @@
           <t>17:38.83</t>
         </is>
       </c>
+      <c r="Q125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R125" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="126" ht="15.95" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -9282,6 +10760,12 @@
           <t>20:08.33</t>
         </is>
       </c>
+      <c r="Q126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R126" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="127" ht="15.95" customHeight="1">
       <c r="A127" s="4" t="n">
@@ -9352,6 +10836,19 @@
           <t>19:07.55</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Poseidon Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="R127" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="128" ht="15.95" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -9422,6 +10919,14 @@
           <t>5:18.88</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Kırklareli</t>
+        </is>
+      </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129" ht="15.95" customHeight="1">
       <c r="A129" s="4" t="n">
@@ -9492,6 +10997,19 @@
           <t>9:05.43</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Lotus Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R129" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" ht="15.95" customHeight="1">
       <c r="A130" s="2" t="n">
@@ -9562,6 +11080,19 @@
           <t>28.32</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Eskişehir Gençlik Ve Spor Il Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R130" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" ht="15.95" customHeight="1">
       <c r="A131" s="4" t="n">
@@ -9632,6 +11163,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Eskisehir Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="15.95" customHeight="1">
       <c r="A132" s="2" t="n">
@@ -9702,6 +11246,19 @@
           <t>1:18.85</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lotus Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R132" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="133" ht="15.95" customHeight="1">
       <c r="A133" s="4" t="n">
@@ -9772,6 +11329,12 @@
           <t>2:22.25</t>
         </is>
       </c>
+      <c r="Q133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R133" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="134" ht="15.95" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -9842,6 +11405,12 @@
           <t>27.35</t>
         </is>
       </c>
+      <c r="Q134" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R134" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="135" ht="15.95" customHeight="1">
       <c r="A135" s="4" t="n">
@@ -9912,6 +11481,12 @@
           <t>2:13.60</t>
         </is>
       </c>
+      <c r="Q135" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R135" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="136" ht="15.95" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -9982,6 +11557,17 @@
           <t>2:44.04</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Eskisehir Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137" ht="15.95" customHeight="1">
       <c r="A137" s="4" t="n">
@@ -10052,6 +11638,19 @@
           <t>28.18</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Eskişehir Gençlik Ve Spor Il Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R137" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="138" ht="15.95" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -10122,6 +11721,19 @@
           <t>2:36.89</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Lotus Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R138" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" ht="15.95" customHeight="1">
       <c r="A139" s="4" t="n">
@@ -10192,6 +11804,14 @@
           <t>2:44.37</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140" ht="15.95" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -10262,6 +11882,19 @@
           <t>1:14.15</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Eskişehir Gençlik Ve Spor Il Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R140" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="141" ht="15.95" customHeight="1">
       <c r="A141" s="4" t="n">
@@ -10332,6 +11965,19 @@
           <t>2:54.94</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Eskisehir Olimpik Kulaclar Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R141" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" ht="15.95" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -10402,6 +12048,12 @@
           <t>2:48.06</t>
         </is>
       </c>
+      <c r="Q142" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R142" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="143" ht="15.95" customHeight="1">
       <c r="A143" s="4" t="n">
@@ -10472,6 +12124,19 @@
           <t>2:51.21</t>
         </is>
       </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Eskişehir Gençlik Ve Spor Il Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="R143" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" ht="15.95" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -10542,6 +12207,12 @@
           <t>2:13.72</t>
         </is>
       </c>
+      <c r="Q144" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R144" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="145" ht="15.95" customHeight="1">
       <c r="A145" s="4" t="n">
@@ -10612,6 +12283,19 @@
           <t>2:40.45</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Gaziantep Şehitkamil Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="R145" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" ht="15.95" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -10678,6 +12362,12 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="Q146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R146" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="147" ht="15.95" customHeight="1">
       <c r="A147" s="4" t="n">
@@ -10748,6 +12438,12 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="Q147" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R147" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="148" ht="15.95" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -10818,6 +12514,19 @@
           <t>2:43.63</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Gaziantep Gençlik Ve Spor İl Müdürlüğü Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="R148" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" ht="15.95" customHeight="1">
       <c r="A149" s="4" t="n">
@@ -10888,6 +12597,19 @@
           <t>2:40.37</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Gaziantep Şehitkamil Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="R149" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" ht="15.95" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -10958,6 +12680,19 @@
           <t>5:33.80</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Turkıye</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="R150" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" ht="15.95" customHeight="1">
       <c r="A151" s="4" t="n">
@@ -10975,7 +12710,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Fatma Berra ÖZER</t>
+          <t>Fatma Berra Özer</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -11027,6 +12762,19 @@
         <is>
           <t>5:21.48</t>
         </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Turkıye</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Gaziantep Şehitkamil Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="R151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152" ht="15.95" customHeight="1">
@@ -11045,7 +12793,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Yağmur KONT</t>
+          <t>Yağmur Kont</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -11097,6 +12845,14 @@
         <is>
           <t>18:40.08</t>
         </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Gaziantep Şehitkamil Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="R152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153" ht="15.95" customHeight="1">
@@ -11168,6 +12924,19 @@
           <t>19:17.65</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Gaziantep Şehitkamil Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="R153" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" ht="15.95" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -11238,6 +13007,19 @@
           <t>2:35.13</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Giresunalfa Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Giresun</t>
+        </is>
+      </c>
+      <c r="R154" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" ht="15.95" customHeight="1">
       <c r="A155" s="4" t="n">
@@ -11308,6 +13090,19 @@
           <t>2:41.59</t>
         </is>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Giresun Yildizlar Takimi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Giresun</t>
+        </is>
+      </c>
+      <c r="R155" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" ht="15.95" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -11378,6 +13173,12 @@
           <t>2:40.01</t>
         </is>
       </c>
+      <c r="Q156" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R156" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="157" ht="15.95" customHeight="1">
       <c r="A157" s="4" t="n">
@@ -11385,7 +13186,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -11447,6 +13248,19 @@
         <is>
           <t>2:24.00</t>
         </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Fenerbahçe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R157" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="158" ht="15.95" customHeight="1">
@@ -11455,7 +13269,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11517,6 +13331,19 @@
         <is>
           <t>26.75</t>
         </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R158" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="159" ht="15.95" customHeight="1">
@@ -11525,7 +13352,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
@@ -11587,6 +13414,12 @@
         <is>
           <t>27.15</t>
         </is>
+      </c>
+      <c r="Q159" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R159" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="160" ht="15.95" customHeight="1">
@@ -11595,7 +13428,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -11657,6 +13490,12 @@
         <is>
           <t>15:51.63</t>
         </is>
+      </c>
+      <c r="Q160" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R160" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="161" ht="15.95" customHeight="1">
@@ -11665,7 +13504,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
@@ -11727,6 +13566,12 @@
         <is>
           <t>4:03.18</t>
         </is>
+      </c>
+      <c r="Q161" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R161" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="162" ht="15.95" customHeight="1">
@@ -11735,7 +13580,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -11797,6 +13642,19 @@
         <is>
           <t>29.81</t>
         </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R162" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="163" ht="15.95" customHeight="1">
@@ -11805,7 +13663,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
@@ -11867,6 +13725,12 @@
         <is>
           <t>4:41.29</t>
         </is>
+      </c>
+      <c r="Q163" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R163" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="164" ht="15.95" customHeight="1">
@@ -11875,7 +13739,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11937,6 +13801,19 @@
         <is>
           <t>5:03.83</t>
         </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165" ht="15.95" customHeight="1">
@@ -11945,7 +13822,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
@@ -12007,6 +13884,19 @@
         <is>
           <t>17:01.28</t>
         </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R165" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="166" ht="15.95" customHeight="1">
@@ -12015,7 +13905,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -12077,6 +13967,19 @@
         <is>
           <t>27.64</t>
         </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R166" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="167" ht="15.95" customHeight="1">
@@ -12085,7 +13988,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
@@ -12139,6 +14042,12 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="Q167" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R167" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="168" ht="15.95" customHeight="1">
@@ -12147,7 +14056,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -12209,6 +14118,12 @@
         <is>
           <t>4:40.49</t>
         </is>
+      </c>
+      <c r="Q168" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R168" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="169" ht="15.95" customHeight="1">
@@ -12217,7 +14132,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
@@ -12275,6 +14190,12 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="Q169" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R169" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="170" ht="15.95" customHeight="1">
@@ -12283,7 +14204,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12345,6 +14266,12 @@
         <is>
           <t>4:38.51</t>
         </is>
+      </c>
+      <c r="Q170" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R170" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="171" ht="15.95" customHeight="1">
@@ -12353,7 +14280,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
@@ -12415,6 +14342,19 @@
         <is>
           <t>2:27.22</t>
         </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R171" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="172" ht="15.95" customHeight="1">
@@ -12423,7 +14363,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12485,6 +14425,19 @@
         <is>
           <t>2:27.11</t>
         </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R172" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="173" ht="15.95" customHeight="1">
@@ -12493,7 +14446,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
@@ -12555,6 +14508,12 @@
         <is>
           <t>16:35.63</t>
         </is>
+      </c>
+      <c r="Q173" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R173" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="174" ht="15.95" customHeight="1">
@@ -12563,7 +14522,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -12625,6 +14584,19 @@
         <is>
           <t>5:30.87</t>
         </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R174" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="175" ht="15.95" customHeight="1">
@@ -12633,7 +14605,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -12695,6 +14667,19 @@
         <is>
           <t>4:58.99</t>
         </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R175" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176" ht="15.95" customHeight="1">
@@ -12703,7 +14688,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -12765,6 +14750,12 @@
         <is>
           <t>25.87</t>
         </is>
+      </c>
+      <c r="Q176" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R176" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="177" ht="15.95" customHeight="1">
@@ -12773,7 +14764,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -12835,6 +14826,19 @@
         <is>
           <t>3:11.89</t>
         </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R177" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="178" ht="15.95" customHeight="1">
@@ -12843,7 +14847,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -12905,6 +14909,12 @@
         <is>
           <t>4:28.21</t>
         </is>
+      </c>
+      <c r="Q178" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R178" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="179" ht="15.95" customHeight="1">
@@ -12913,7 +14923,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -12975,6 +14985,19 @@
         <is>
           <t>2:23.91</t>
         </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Fenerbahçe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R179" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="180" ht="15.95" customHeight="1">
@@ -12983,7 +15006,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -13045,6 +15068,19 @@
         <is>
           <t>1:05.53</t>
         </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Fenerbahçe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R180" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="181" ht="15.95" customHeight="1">
@@ -13053,7 +15089,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -13115,6 +15151,12 @@
         <is>
           <t>2:16.79</t>
         </is>
+      </c>
+      <c r="Q181" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R181" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="182" ht="15.95" customHeight="1">
@@ -13123,7 +15165,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -13185,6 +15227,19 @@
         <is>
           <t>5:05.54</t>
         </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Fenerbahçe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R182" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="183" ht="15.95" customHeight="1">
@@ -13193,7 +15248,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -13255,6 +15310,19 @@
         <is>
           <t>26.93</t>
         </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R183" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="184" ht="15.95" customHeight="1">
@@ -13263,7 +15331,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -13325,6 +15393,19 @@
         <is>
           <t>16:19.78</t>
         </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R184" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="185" ht="15.95" customHeight="1">
@@ -13333,7 +15414,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
@@ -13395,6 +15476,12 @@
         <is>
           <t>4:07.09</t>
         </is>
+      </c>
+      <c r="Q185" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R185" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="186" ht="15.95" customHeight="1">
@@ -13403,7 +15490,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -13465,6 +15552,12 @@
         <is>
           <t>2:09.10</t>
         </is>
+      </c>
+      <c r="Q186" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R186" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="187" ht="15.95" customHeight="1">
@@ -13473,7 +15566,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
@@ -13535,6 +15628,19 @@
         <is>
           <t>4:33.81</t>
         </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R187" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="188" ht="15.95" customHeight="1">
@@ -13543,7 +15649,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -13601,6 +15707,12 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="Q188" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R188" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="189" ht="15.95" customHeight="1">
@@ -13609,7 +15721,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -13671,6 +15783,12 @@
         <is>
           <t>2:09.28</t>
         </is>
+      </c>
+      <c r="Q189" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R189" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="190" ht="15.95" customHeight="1">
@@ -13679,7 +15797,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -13741,6 +15859,19 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R190" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="191" ht="15.95" customHeight="1">
@@ -13749,7 +15880,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
@@ -13811,6 +15942,19 @@
         <is>
           <t>5:43.98</t>
         </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R191" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="192" ht="15.95" customHeight="1">
@@ -13819,7 +15963,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -13877,6 +16021,12 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="Q192" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R192" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="193" ht="15.95" customHeight="1">
@@ -13885,7 +16035,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -13947,6 +16097,19 @@
         <is>
           <t>2:36.48</t>
         </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Fenerbahçe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R193" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="194" ht="15.95" customHeight="1">
@@ -13955,7 +16118,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -14017,6 +16180,19 @@
         <is>
           <t>1:54.46</t>
         </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R194" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="195" ht="15.95" customHeight="1">
@@ -14025,7 +16201,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -14087,6 +16263,12 @@
         <is>
           <t>29.72</t>
         </is>
+      </c>
+      <c r="Q195" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R195" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="196" ht="15.95" customHeight="1">
@@ -14095,7 +16277,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -14157,6 +16339,19 @@
         <is>
           <t>1:08.26</t>
         </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R196" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="197" ht="15.95" customHeight="1">
@@ -14165,7 +16360,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -14227,6 +16422,12 @@
         <is>
           <t>5:08.67</t>
         </is>
+      </c>
+      <c r="Q197" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R197" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="198" ht="15.95" customHeight="1">
@@ -14235,7 +16436,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -14297,6 +16498,19 @@
         <is>
           <t>30.40</t>
         </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>İstek Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R198" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="199" ht="15.95" customHeight="1">
@@ -14305,7 +16519,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
@@ -14367,6 +16581,12 @@
         <is>
           <t>2:20.49</t>
         </is>
+      </c>
+      <c r="Q199" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R199" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="200" ht="15.95" customHeight="1">
@@ -14375,7 +16595,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -14437,6 +16657,19 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R200" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="201" ht="15.95" customHeight="1">
@@ -14445,7 +16678,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
@@ -14507,6 +16740,19 @@
         <is>
           <t>2:43.76</t>
         </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R201" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="202" ht="15.95" customHeight="1">
@@ -14515,7 +16761,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -14577,6 +16823,12 @@
         <is>
           <t>4:55.94</t>
         </is>
+      </c>
+      <c r="Q202" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R202" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="203" ht="15.95" customHeight="1">
@@ -14585,7 +16837,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
@@ -14647,6 +16899,19 @@
         <is>
           <t>2:48.20</t>
         </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R203" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="204" ht="15.95" customHeight="1">
@@ -14655,7 +16920,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -14717,6 +16982,19 @@
         <is>
           <t>5:13.13</t>
         </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Galatasaray Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R204" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="205" ht="15.95" customHeight="1">
@@ -14725,7 +17003,7 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
@@ -14787,6 +17065,19 @@
         <is>
           <t>5:26.13</t>
         </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Atletico Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R205" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="206" ht="15.95" customHeight="1">
@@ -14795,7 +17086,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -14857,6 +17148,12 @@
         <is>
           <t>29.15</t>
         </is>
+      </c>
+      <c r="Q206" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R206" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="207" ht="15.95" customHeight="1">
@@ -14865,7 +17162,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
@@ -14927,6 +17224,19 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R207" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="208" ht="15.95" customHeight="1">
@@ -14935,7 +17245,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -14997,6 +17307,12 @@
         <is>
           <t>2:04.95</t>
         </is>
+      </c>
+      <c r="Q208" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R208" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="209" ht="15.95" customHeight="1">
@@ -15005,7 +17321,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
@@ -15067,6 +17383,19 @@
         <is>
           <t>2:50.01</t>
         </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Izmir Yüzme İhtisas Ve Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R209" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="210" ht="15.95" customHeight="1">
@@ -15075,7 +17404,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -15137,6 +17466,19 @@
         <is>
           <t>2:50.30</t>
         </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Dokuz Eylül Üniversitesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R210" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="211" ht="15.95" customHeight="1">
@@ -15145,7 +17487,7 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
@@ -15207,6 +17549,19 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R211" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="212" ht="15.95" customHeight="1">
@@ -15215,7 +17570,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -15277,6 +17632,17 @@
         <is>
           <t>5:51.23</t>
         </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Ege Ocean Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="213" ht="15.95" customHeight="1">
@@ -15285,7 +17651,7 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
@@ -15347,6 +17713,19 @@
         <is>
           <t>2:35.32</t>
         </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Izmir Yüzme İhtisas Ve Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R213" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="214" ht="15.95" customHeight="1">
@@ -15355,7 +17734,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -15417,6 +17796,19 @@
         <is>
           <t>2:55.74</t>
         </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Dokuz Eylül Üniversitesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R214" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="215" ht="15.95" customHeight="1">
@@ -15425,7 +17817,7 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
@@ -15487,6 +17879,19 @@
         <is>
           <t>2:22.79</t>
         </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Rota Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R215" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="216" ht="15.95" customHeight="1">
@@ -15495,7 +17900,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -15557,6 +17962,19 @@
         <is>
           <t>1:04.68</t>
         </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Atletico Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R216" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="217" ht="15.95" customHeight="1">
@@ -15565,7 +17983,7 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
@@ -15627,6 +18045,19 @@
         <is>
           <t>4:48.73</t>
         </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R217" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="218" ht="15.95" customHeight="1">
@@ -15635,7 +18066,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -15697,6 +18128,12 @@
         <is>
           <t>58.38</t>
         </is>
+      </c>
+      <c r="Q218" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R218" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="219" ht="15.95" customHeight="1">
@@ -15705,7 +18142,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
@@ -15767,6 +18204,19 @@
         <is>
           <t>2:27.34</t>
         </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Rota Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R219" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="220" ht="15.95" customHeight="1">
@@ -15775,7 +18225,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -15837,6 +18287,19 @@
         <is>
           <t>2:45.97</t>
         </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Dokuz Eylül Üniversitesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R220" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="221" ht="15.95" customHeight="1">
@@ -15845,7 +18308,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -15907,6 +18370,19 @@
         <is>
           <t>2:27.96</t>
         </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Dokuz Eylül Üniversitesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R221" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="222" ht="15.95" customHeight="1">
@@ -15915,7 +18391,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -15977,15 +18453,28 @@
         <is>
           <t>5:28.15</t>
         </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Dalton Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R222" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="223" ht="15.95" customHeight="1">
       <c r="A223" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>Izmir</t>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
@@ -16047,6 +18536,19 @@
         <is>
           <t>2:22.59</t>
         </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Izmir Yüzme İhtisas Ve Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R223" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="224" ht="15.95" customHeight="1">
@@ -16055,7 +18557,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -16065,7 +18567,7 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Ç. ÇOLAKOĞULLARI</t>
+          <t>Çağdaş Çolakoğulları</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -16117,6 +18619,12 @@
         <is>
           <t>25.88</t>
         </is>
+      </c>
+      <c r="Q224" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R224" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="225" ht="15.95" customHeight="1">
@@ -16125,7 +18633,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
@@ -16187,6 +18695,19 @@
         <is>
           <t>2:58.11</t>
         </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Alsancak 35 Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R225" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="226" ht="15.95" customHeight="1">
@@ -16195,7 +18716,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -16257,6 +18778,12 @@
         <is>
           <t>1:04.72</t>
         </is>
+      </c>
+      <c r="Q226" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R226" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="227" ht="15.95" customHeight="1">
@@ -16265,7 +18792,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
@@ -16327,6 +18854,19 @@
         <is>
           <t>2:50.76</t>
         </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Atletico Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R227" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228" ht="15.95" customHeight="1">
@@ -16335,7 +18875,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -16397,6 +18937,12 @@
         <is>
           <t>2:25.17</t>
         </is>
+      </c>
+      <c r="Q228" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R228" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="229" ht="15.95" customHeight="1">
@@ -16405,7 +18951,7 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
@@ -16467,6 +19013,19 @@
         <is>
           <t>5:37.38</t>
         </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Atletico Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R229" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="230" ht="15.95" customHeight="1">
@@ -16475,7 +19034,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -16537,6 +19096,19 @@
         <is>
           <t>6:23.01</t>
         </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Ege Ocean Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R230" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="231" ht="15.95" customHeight="1">
@@ -16545,7 +19117,7 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
@@ -16607,6 +19179,19 @@
         <is>
           <t>2:50.65</t>
         </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Ege Ocean Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R231" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="232" ht="15.95" customHeight="1">
@@ -16615,7 +19200,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -16677,6 +19262,19 @@
         <is>
           <t>5:42.40</t>
         </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Ege Ocean Yüzme İhtisas Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R232" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="233" ht="15.95" customHeight="1">
@@ -16685,7 +19283,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
@@ -16747,6 +19345,19 @@
         <is>
           <t>5:20.05</t>
         </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Atletico Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R233" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="234" ht="15.95" customHeight="1">
@@ -16755,7 +19366,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -16817,6 +19428,12 @@
         <is>
           <t>2:23.28</t>
         </is>
+      </c>
+      <c r="Q234" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R234" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="235" ht="15.95" customHeight="1">
@@ -16825,7 +19442,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
@@ -16887,6 +19504,19 @@
         <is>
           <t>5:14.28</t>
         </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R235" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="236" ht="15.95" customHeight="1">
@@ -16895,7 +19525,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -16957,6 +19587,19 @@
         <is>
           <t>NT</t>
         </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R236" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="237" ht="15.95" customHeight="1">
@@ -16965,7 +19608,7 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
@@ -17027,6 +19670,19 @@
         <is>
           <t>1:20.06</t>
         </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>İzmir Ferdi</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R237" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="238" ht="15.95" customHeight="1">
@@ -17035,7 +19691,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Izmir</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -17097,6 +19753,19 @@
         <is>
           <t>2:46.15</t>
         </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Goztepe Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="R238" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="239" ht="15.95" customHeight="1">
@@ -17168,6 +19837,19 @@
           <t>19:37.39</t>
         </is>
       </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Kayseri Atak Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R239" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="240" ht="15.95" customHeight="1">
       <c r="A240" s="2" t="n">
@@ -17238,6 +19920,19 @@
           <t>5:11.71</t>
         </is>
       </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Anadolu Yildizlari Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R240" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="241" ht="15.95" customHeight="1">
       <c r="A241" s="4" t="n">
@@ -17304,6 +19999,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Kayseri Fırtına Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R241" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="242" ht="15.95" customHeight="1">
       <c r="A242" s="2" t="n">
@@ -17374,6 +20082,19 @@
           <t>2:47.50</t>
         </is>
       </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Kayseri Spor A.Ş. Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R242" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="243" ht="15.95" customHeight="1">
       <c r="A243" s="4" t="n">
@@ -17444,6 +20165,12 @@
           <t>16:33.80</t>
         </is>
       </c>
+      <c r="Q243" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R243" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="244" ht="15.95" customHeight="1">
       <c r="A244" s="2" t="n">
@@ -17514,6 +20241,19 @@
           <t>17:53.76</t>
         </is>
       </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Kayseri Atak Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R244" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="245" ht="15.95" customHeight="1">
       <c r="A245" s="4" t="n">
@@ -17584,6 +20324,19 @@
           <t>2:34.05</t>
         </is>
       </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Kayseri Okyanus Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R245" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="246" ht="15.95" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -17654,6 +20407,19 @@
           <t>2:24.73</t>
         </is>
       </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Kayseri Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R246" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="247" ht="15.95" customHeight="1">
       <c r="A247" s="4" t="n">
@@ -17724,6 +20490,12 @@
           <t>15:54.98</t>
         </is>
       </c>
+      <c r="Q247" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R247" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="248" ht="15.95" customHeight="1">
       <c r="A248" s="2" t="n">
@@ -17794,6 +20566,12 @@
           <t>15:56.45</t>
         </is>
       </c>
+      <c r="Q248" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R248" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="249" ht="15.95" customHeight="1">
       <c r="A249" s="4" t="n">
@@ -17864,6 +20642,19 @@
           <t>16:37.82</t>
         </is>
       </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Erciyes Yıldız Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R249" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="250" ht="15.95" customHeight="1">
       <c r="A250" s="2" t="n">
@@ -17934,6 +20725,19 @@
           <t>18:38.95</t>
         </is>
       </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Kayseri Atak Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R250" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="251" ht="15.95" customHeight="1">
       <c r="A251" s="4" t="n">
@@ -18004,6 +20808,12 @@
           <t>17:27.91</t>
         </is>
       </c>
+      <c r="Q251" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R251" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="252" ht="15.95" customHeight="1">
       <c r="A252" s="2" t="n">
@@ -18074,6 +20884,19 @@
           <t>2:43.06</t>
         </is>
       </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Lidya Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R252" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="253" ht="15.95" customHeight="1">
       <c r="A253" s="4" t="n">
@@ -18140,6 +20963,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Kayseri Fırtına Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R253" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="254" ht="15.95" customHeight="1">
       <c r="A254" s="2" t="n">
@@ -18210,6 +21046,12 @@
           <t>2:07.52</t>
         </is>
       </c>
+      <c r="Q254" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R254" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="255" ht="15.95" customHeight="1">
       <c r="A255" s="4" t="n">
@@ -18280,6 +21122,19 @@
           <t>2:37.29</t>
         </is>
       </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Kocaeli Yıldızlar Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="R255" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="256" ht="15.95" customHeight="1">
       <c r="A256" s="2" t="n">
@@ -18350,6 +21205,12 @@
           <t>18:30.87</t>
         </is>
       </c>
+      <c r="Q256" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R256" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="257" ht="15.95" customHeight="1">
       <c r="A257" s="4" t="n">
@@ -18420,6 +21281,17 @@
           <t>11:17.69</t>
         </is>
       </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Ilker Alkaranli Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="258" ht="15.95" customHeight="1">
       <c r="A258" s="2" t="n">
@@ -18490,6 +21362,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Albatros Yüzme Akademisi</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="R258" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="259" ht="15.95" customHeight="1">
       <c r="A259" s="4" t="n">
@@ -18560,6 +21445,12 @@
           <t>2:25.69</t>
         </is>
       </c>
+      <c r="Q259" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R259" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="260" ht="15.95" customHeight="1">
       <c r="A260" s="2" t="n">
@@ -18630,6 +21521,19 @@
           <t>5:09.56</t>
         </is>
       </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R260" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="261" ht="15.95" customHeight="1">
       <c r="A261" s="4" t="n">
@@ -18700,6 +21604,19 @@
           <t>5:48.05</t>
         </is>
       </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R261" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="262" ht="15.95" customHeight="1">
       <c r="A262" s="2" t="n">
@@ -18770,6 +21687,19 @@
           <t>4:45.54</t>
         </is>
       </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Ted Mersin Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R262" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="263" ht="15.95" customHeight="1">
       <c r="A263" s="4" t="n">
@@ -18840,6 +21770,19 @@
           <t>5:06.28</t>
         </is>
       </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Gelecek Gençlik Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R263" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="264" ht="15.95" customHeight="1">
       <c r="A264" s="2" t="n">
@@ -18910,6 +21853,19 @@
           <t>5:54.08</t>
         </is>
       </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R264" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="265" ht="15.95" customHeight="1">
       <c r="A265" s="4" t="n">
@@ -18980,6 +21936,19 @@
           <t>4:59.25</t>
         </is>
       </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Ted Mersin Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R265" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="266" ht="15.95" customHeight="1">
       <c r="A266" s="2" t="n">
@@ -19050,6 +22019,19 @@
           <t>5:23.09</t>
         </is>
       </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R266" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="267" ht="15.95" customHeight="1">
       <c r="A267" s="4" t="n">
@@ -19120,6 +22102,19 @@
           <t>5:37.16</t>
         </is>
       </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R267" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="268" ht="15.95" customHeight="1">
       <c r="A268" s="2" t="n">
@@ -19190,6 +22185,19 @@
           <t>5:48.57</t>
         </is>
       </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Mersin Egitim Vakfi Toros Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R268" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="269" ht="15.95" customHeight="1">
       <c r="A269" s="4" t="n">
@@ -19252,6 +22260,12 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="Q269" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R269" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="270" ht="15.95" customHeight="1">
       <c r="A270" s="2" t="n">
@@ -19322,6 +22336,19 @@
           <t>5:11.78</t>
         </is>
       </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Ted Mersin Koleji Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R270" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="271" ht="15.95" customHeight="1">
       <c r="A271" s="4" t="n">
@@ -19392,6 +22419,19 @@
           <t>2:47.33</t>
         </is>
       </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Mersin Gençlerbirliği Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="R271" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="272" ht="15.95" customHeight="1">
       <c r="A272" s="2" t="n">
@@ -19462,6 +22502,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Altinkulac Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Sakarya</t>
+        </is>
+      </c>
+      <c r="R272" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="273" ht="15.95" customHeight="1">
       <c r="A273" s="4" t="n">
@@ -19532,6 +22585,12 @@
           <t>28.74</t>
         </is>
       </c>
+      <c r="Q273" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R273" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="274" ht="15.95" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -19602,6 +22661,19 @@
           <t>2:41.28</t>
         </is>
       </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Sakarya Aqua Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Sakarya</t>
+        </is>
+      </c>
+      <c r="R274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="275" ht="15.95" customHeight="1">
       <c r="A275" s="4" t="n">
@@ -19672,6 +22744,19 @@
           <t>2:42.21</t>
         </is>
       </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Hendek Olimpik Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Sakarya</t>
+        </is>
+      </c>
+      <c r="R275" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="276" ht="15.95" customHeight="1">
       <c r="A276" s="2" t="n">
@@ -19742,6 +22827,19 @@
           <t>2:35.49</t>
         </is>
       </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R276" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="277" ht="15.95" customHeight="1">
       <c r="A277" s="4" t="n">
@@ -19812,6 +22910,19 @@
           <t>1:07.81</t>
         </is>
       </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R277" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="278" ht="15.95" customHeight="1">
       <c r="A278" s="2" t="n">
@@ -19882,6 +22993,12 @@
           <t>4:56.91</t>
         </is>
       </c>
+      <c r="Q278" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R278" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="279" ht="15.95" customHeight="1">
       <c r="A279" s="4" t="n">
@@ -19952,6 +23069,12 @@
           <t>2:25.57</t>
         </is>
       </c>
+      <c r="Q279" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R279" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="280" ht="15.95" customHeight="1">
       <c r="A280" s="2" t="n">
@@ -20022,6 +23145,12 @@
           <t>8:26.02</t>
         </is>
       </c>
+      <c r="Q280" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R280" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="281" ht="15.95" customHeight="1">
       <c r="A281" s="4" t="n">
@@ -20092,6 +23221,12 @@
           <t>2:44.43</t>
         </is>
       </c>
+      <c r="Q281" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R281" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="282" ht="15.95" customHeight="1">
       <c r="A282" s="2" t="n">
@@ -20162,6 +23297,19 @@
           <t>2:40.63</t>
         </is>
       </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R282" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="283" ht="15.95" customHeight="1">
       <c r="A283" s="4" t="n">
@@ -20232,6 +23380,19 @@
           <t>2:30.88</t>
         </is>
       </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R283" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="284" ht="15.95" customHeight="1">
       <c r="A284" s="2" t="n">
@@ -20302,6 +23463,19 @@
           <t>5:13.43</t>
         </is>
       </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Temel Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R284" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="285" ht="15.95" customHeight="1">
       <c r="A285" s="4" t="n">
@@ -20372,6 +23546,19 @@
           <t>2:33.65</t>
         </is>
       </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R285" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="286" ht="15.95" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -20442,6 +23629,19 @@
           <t>2:43.57</t>
         </is>
       </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R286" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="287" ht="15.95" customHeight="1">
       <c r="A287" s="4" t="n">
@@ -20512,6 +23712,19 @@
           <t>2:43.03</t>
         </is>
       </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Sure Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R287" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="288" ht="15.95" customHeight="1">
       <c r="A288" s="2" t="n">
@@ -20582,6 +23795,19 @@
           <t>2:41.05</t>
         </is>
       </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R288" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="289" ht="15.95" customHeight="1">
       <c r="A289" s="4" t="n">
@@ -20652,6 +23878,19 @@
           <t>2:20.59</t>
         </is>
       </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R289" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="290" ht="15.95" customHeight="1">
       <c r="A290" s="2" t="n">
@@ -20722,6 +23961,12 @@
           <t>8:41.84</t>
         </is>
       </c>
+      <c r="Q290" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R290" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="291" ht="15.95" customHeight="1">
       <c r="A291" s="4" t="n">
@@ -20792,6 +24037,19 @@
           <t>2:39.58</t>
         </is>
       </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Temel Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R291" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="292" ht="15.95" customHeight="1">
       <c r="A292" s="2" t="n">
@@ -20862,6 +24120,19 @@
           <t>4:57.58</t>
         </is>
       </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R292" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="293" ht="15.95" customHeight="1">
       <c r="A293" s="4" t="n">
@@ -20932,6 +24203,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R293" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="294" ht="15.95" customHeight="1">
       <c r="A294" s="2" t="n">
@@ -21002,6 +24286,19 @@
           <t>2:37.63</t>
         </is>
       </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Temel Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R294" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="295" ht="15.95" customHeight="1">
       <c r="A295" s="4" t="n">
@@ -21072,6 +24369,19 @@
           <t>18:31.97</t>
         </is>
       </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R295" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="296" ht="15.95" customHeight="1">
       <c r="A296" s="2" t="n">
@@ -21142,6 +24452,19 @@
           <t>2:47.14</t>
         </is>
       </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R296" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="297" ht="15.95" customHeight="1">
       <c r="A297" s="4" t="n">
@@ -21212,6 +24535,19 @@
           <t>2:51.59</t>
         </is>
       </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R297" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="298" ht="15.95" customHeight="1">
       <c r="A298" s="2" t="n">
@@ -21282,6 +24618,19 @@
           <t>2:50.18</t>
         </is>
       </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Temel Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R298" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="299" ht="15.95" customHeight="1">
       <c r="A299" s="4" t="n">
@@ -21352,6 +24701,19 @@
           <t>6:11.73</t>
         </is>
       </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Temel Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R299" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="300" ht="15.95" customHeight="1">
       <c r="A300" s="2" t="n">
@@ -21422,6 +24784,19 @@
           <t>2:34.32</t>
         </is>
       </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>Samsun Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R300" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="301" ht="15.95" customHeight="1">
       <c r="A301" s="4" t="n">
@@ -21492,6 +24867,19 @@
           <t>2:43.63</t>
         </is>
       </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R301" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="302" ht="15.95" customHeight="1">
       <c r="A302" s="2" t="n">
@@ -21562,6 +24950,14 @@
           <t>2:49.04</t>
         </is>
       </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Giresun</t>
+        </is>
+      </c>
+      <c r="R302" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="303" ht="15.95" customHeight="1">
       <c r="A303" s="4" t="n">
@@ -21632,6 +25028,19 @@
           <t>2:37.00</t>
         </is>
       </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Yildiz Su Sporları Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Samsun</t>
+        </is>
+      </c>
+      <c r="R303" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="304" ht="15.95" customHeight="1">
       <c r="A304" s="2" t="n">
@@ -21702,6 +25111,19 @@
           <t>4:35.43</t>
         </is>
       </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Tekirdag Ayyildiz Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R304" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="305" ht="15.95" customHeight="1">
       <c r="A305" s="4" t="n">
@@ -21772,6 +25194,12 @@
           <t>4:03.84</t>
         </is>
       </c>
+      <c r="Q305" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R305" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="306" ht="15.95" customHeight="1">
       <c r="A306" s="2" t="n">
@@ -21842,6 +25270,12 @@
           <t>58.36</t>
         </is>
       </c>
+      <c r="Q306" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R306" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="307" ht="15.95" customHeight="1">
       <c r="A307" s="4" t="n">
@@ -21912,6 +25346,19 @@
           <t>2:25.82</t>
         </is>
       </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Teyik Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R307" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="308" ht="15.95" customHeight="1">
       <c r="A308" s="2" t="n">
@@ -21978,6 +25425,12 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="Q308" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R308" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="309" ht="15.95" customHeight="1">
       <c r="A309" s="4" t="n">
@@ -22048,6 +25501,19 @@
           <t>10:21.55</t>
         </is>
       </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Çorlu Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R309" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="310" ht="15.95" customHeight="1">
       <c r="A310" s="2" t="n">
@@ -22118,6 +25584,19 @@
           <t>5:40.64</t>
         </is>
       </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Çorlu Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R310" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="311" ht="15.95" customHeight="1">
       <c r="A311" s="4" t="n">
@@ -22188,6 +25667,19 @@
           <t>18:33.04</t>
         </is>
       </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Çorlu Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R311" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="312" ht="15.95" customHeight="1">
       <c r="A312" s="2" t="n">
@@ -22258,6 +25750,14 @@
           <t>5:09.68</t>
         </is>
       </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R312" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="313" ht="15.95" customHeight="1">
       <c r="A313" s="4" t="n">
@@ -22328,6 +25828,19 @@
           <t>2:32.32</t>
         </is>
       </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Çorlu Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R313" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="314" ht="15.95" customHeight="1">
       <c r="A314" s="2" t="n">
@@ -22398,6 +25911,19 @@
           <t>1:06.45</t>
         </is>
       </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>Ferdi</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R314" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="315" ht="15.95" customHeight="1">
       <c r="A315" s="4" t="n">
@@ -22468,6 +25994,19 @@
           <t>5:28.85</t>
         </is>
       </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Tekirdag Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R315" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="316" ht="15.95" customHeight="1">
       <c r="A316" s="2" t="n">
@@ -22538,6 +26077,14 @@
           <t>1:04.96</t>
         </is>
       </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R316" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="317" ht="15.95" customHeight="1">
       <c r="A317" s="4" t="n">
@@ -22608,6 +26155,19 @@
           <t>20:14.74</t>
         </is>
       </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Çorlu Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="R317" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="318" ht="15.95" customHeight="1">
       <c r="A318" s="2" t="n">
@@ -22678,6 +26238,19 @@
           <t>6:07.44</t>
         </is>
       </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Tokat Gaziosmanpasa Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Tokat</t>
+        </is>
+      </c>
+      <c r="R318" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="319" ht="15.95" customHeight="1">
       <c r="A319" s="4" t="n">
@@ -22748,6 +26321,19 @@
           <t>6:10.57</t>
         </is>
       </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Tokat Gaziosmanpasa Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R319" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="320" ht="15.95" customHeight="1">
       <c r="A320" s="2" t="n">
@@ -22818,6 +26404,19 @@
           <t>6:18.29</t>
         </is>
       </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Tokat Gaziosmanpasa Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Tokat</t>
+        </is>
+      </c>
+      <c r="R320" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="321" ht="15.95" customHeight="1">
       <c r="A321" s="4" t="n">
@@ -22888,6 +26487,19 @@
           <t>2:46.71</t>
         </is>
       </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R321" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="322" ht="15.95" customHeight="1">
       <c r="A322" s="2" t="n">
@@ -22958,6 +26570,19 @@
           <t>2:41.31</t>
         </is>
       </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R322" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="323" ht="15.95" customHeight="1">
       <c r="A323" s="4" t="n">
@@ -23028,6 +26653,19 @@
           <t>2:14.75</t>
         </is>
       </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Trabzon Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R323" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="324" ht="15.95" customHeight="1">
       <c r="A324" s="2" t="n">
@@ -23098,6 +26736,19 @@
           <t>9:14.44</t>
         </is>
       </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R324" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="325" ht="15.95" customHeight="1">
       <c r="A325" s="4" t="n">
@@ -23160,6 +26811,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Trabzon Yesilova Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R325" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="326" ht="15.95" customHeight="1">
       <c r="A326" s="2" t="n">
@@ -23230,6 +26894,19 @@
           <t>10:15.24</t>
         </is>
       </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Trabzon Arena Yüzme Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R326" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="327" ht="15.95" customHeight="1">
       <c r="A327" s="4" t="n">
@@ -23300,6 +26977,19 @@
           <t>2:46.69</t>
         </is>
       </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R327" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="328" ht="15.95" customHeight="1">
       <c r="A328" s="2" t="n">
@@ -23370,6 +27060,19 @@
           <t>5:51.02</t>
         </is>
       </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R328" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="329" ht="15.95" customHeight="1">
       <c r="A329" s="4" t="n">
@@ -23440,6 +27143,19 @@
           <t>2:26.89</t>
         </is>
       </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R329" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="330" ht="15.95" customHeight="1">
       <c r="A330" s="2" t="n">
@@ -23510,6 +27226,17 @@
           <t>2:45.18</t>
         </is>
       </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>Trabzon Buyuksehir Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>0</v>
+      </c>
+      <c r="R330" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="331" ht="15.95" customHeight="1">
       <c r="A331" s="4" t="n">
@@ -23580,6 +27307,17 @@
           <t>2:42.80</t>
         </is>
       </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Trabzon Buyuksehir Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>0</v>
+      </c>
+      <c r="R331" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="332" ht="15.95" customHeight="1">
       <c r="A332" s="2" t="n">
@@ -23650,6 +27388,19 @@
           <t>5:12.53</t>
         </is>
       </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R332" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="333" ht="15.95" customHeight="1">
       <c r="A333" s="4" t="n">
@@ -23720,6 +27471,19 @@
           <t>2:43.81</t>
         </is>
       </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R333" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="334" ht="15.95" customHeight="1">
       <c r="A334" s="2" t="n">
@@ -23790,6 +27554,19 @@
           <t>10:09.71</t>
         </is>
       </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R334" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="335" ht="15.95" customHeight="1">
       <c r="A335" s="4" t="n">
@@ -23860,6 +27637,19 @@
           <t>5:52.57</t>
         </is>
       </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Trabzon Okyanus Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R335" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="336" ht="15.95" customHeight="1">
       <c r="A336" s="2" t="n">
@@ -23930,6 +27720,19 @@
           <t>5:14.03</t>
         </is>
       </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R336" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="337" ht="15.95" customHeight="1">
       <c r="A337" s="4" t="n">
@@ -24000,6 +27803,19 @@
           <t>2:30.79</t>
         </is>
       </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R337" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="338" ht="15.95" customHeight="1">
       <c r="A338" s="2" t="n">
@@ -24070,6 +27886,19 @@
           <t>2:52.24</t>
         </is>
       </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R338" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="339" ht="15.95" customHeight="1">
       <c r="A339" s="4" t="n">
@@ -24140,6 +27969,12 @@
           <t>2:30.46</t>
         </is>
       </c>
+      <c r="Q339" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R339" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="340" ht="15.95" customHeight="1">
       <c r="A340" s="2" t="n">
@@ -24210,6 +28045,17 @@
           <t>1:14.28</t>
         </is>
       </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Trabzon Buyuksehir Belediyesi Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>0</v>
+      </c>
+      <c r="R340" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="341" ht="15.95" customHeight="1">
       <c r="A341" s="4" t="n">
@@ -24280,6 +28126,19 @@
           <t>2:48.79</t>
         </is>
       </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Tswim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Trabzon</t>
+        </is>
+      </c>
+      <c r="R341" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="342" ht="15.95" customHeight="1">
       <c r="A342" s="2" t="n">
@@ -24350,6 +28209,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Içdaş Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R342" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="343" ht="15.95" customHeight="1">
       <c r="A343" s="4" t="n">
@@ -24420,6 +28292,19 @@
           <t>2:49.58</t>
         </is>
       </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Içdaş Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R343" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="344" ht="15.95" customHeight="1">
       <c r="A344" s="2" t="n">
@@ -24490,6 +28375,19 @@
           <t>2:50.72</t>
         </is>
       </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Çanakkale Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R344" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="345" ht="15.95" customHeight="1">
       <c r="A345" s="4" t="n">
@@ -24560,6 +28458,19 @@
           <t>6:00.13</t>
         </is>
       </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Çanakkale Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R345" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="346" ht="15.95" customHeight="1">
       <c r="A346" s="2" t="n">
@@ -24630,6 +28541,19 @@
           <t>2:50.94</t>
         </is>
       </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Çanakkale Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R346" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="347" ht="15.95" customHeight="1">
       <c r="A347" s="4" t="n">
@@ -24700,6 +28624,19 @@
           <t>NT</t>
         </is>
       </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Çanakkale Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R347" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="348" ht="15.95" customHeight="1">
       <c r="A348" s="2" t="n">
@@ -24770,6 +28707,19 @@
           <t>2:47.61</t>
         </is>
       </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Biga Gelisim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R348" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="349" ht="15.95" customHeight="1">
       <c r="A349" s="4" t="n">
@@ -24840,6 +28790,19 @@
           <t>2:40.90</t>
         </is>
       </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Biga Gelisim Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Çanakkale</t>
+        </is>
+      </c>
+      <c r="R349" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="350" ht="15.95" customHeight="1">
       <c r="A350" s="2" t="n">
@@ -24910,9 +28873,20 @@
           <t>19:45.31</t>
         </is>
       </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Çanakkale Belediye Spor Kulübü</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N350"/>
+  <autoFilter ref="A1:U350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Ömer Selman KARAKÖSE</t>
+          <t>Ömer Selman Karaköse</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Başak İrem ALTUNZİNCİR</t>
+          <t>Başak İrem Altunzincir</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -48781,16 +48781,8 @@
           <t>69913227489</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>? Serbest</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
           <t>100m Kelebek</t>
@@ -49047,7 +49039,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>? Serbest</t>
+          <t>1500m Serbest</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -64089,7 +64081,7 @@
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>? Serbest</t>
+          <t>1500m Serbest</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -48781,8 +48781,16 @@
           <t>69913227489</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>800m Serbest</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
           <t>100m Kelebek</t>

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -54587,7 +54587,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>1500m Serbest</t>
+          <t>800m Serbest</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -45579,7 +45579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T350"/>
+  <dimension ref="A1:T353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -76415,6 +76415,223 @@
         <v/>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Bayan</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Ceren TUNCAY</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>100m Serbest</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>1:03.29</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>100m Kurbağalama</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>1:21.82</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>50m Serbest</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>28.72</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="R351">
+        <f>Q351=B351</f>
+        <v/>
+      </c>
+      <c r="T351">
+        <f>MATCH(D351,[1]Manual!$A:$A,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Bayan</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Öykü AKÇORA</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>100m Serbest</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>59.19</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>50m Sırtüstü</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>30.88</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>100m Sırtüstü</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>1:05.40</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R352">
+        <f>Q352=B352</f>
+        <v/>
+      </c>
+      <c r="T352">
+        <f>MATCH(D352,[1]Manual!$A:$A,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Erkek</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Sarp Barkın HASAY</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>100m Kelebek</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>57.09</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>50m Sırtüstü</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>200m Sırtüstü</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2:05.72</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>100m Sırtüstü</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>57.28</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="R353">
+        <f>Q353=B353</f>
+        <v/>
+      </c>
+      <c r="T353">
+        <f>MATCH(D353,[1]Manual!$A:$A,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -57742,7 +57742,7 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Eskişehir</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
@@ -59332,7 +59332,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -59402,7 +59402,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R157">
@@ -59420,7 +59420,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -59490,7 +59490,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R158">
@@ -59508,7 +59508,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
@@ -59578,7 +59578,7 @@
       </c>
       <c r="Q159" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R159">
@@ -59596,7 +59596,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -59666,7 +59666,7 @@
       </c>
       <c r="Q160" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R160">
@@ -59684,7 +59684,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
@@ -59754,7 +59754,7 @@
       </c>
       <c r="Q161" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="R161">
@@ -59860,7 +59860,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
@@ -59930,7 +59930,7 @@
       </c>
       <c r="Q163" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R163">
@@ -59948,7 +59948,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -60018,7 +60018,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R164">
@@ -60036,7 +60036,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R165">
@@ -60124,7 +60124,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -60194,7 +60194,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="R166">
@@ -60212,7 +60212,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
@@ -60274,7 +60274,7 @@
       </c>
       <c r="Q167" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="R167">
@@ -60292,7 +60292,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -60362,7 +60362,7 @@
       </c>
       <c r="Q168" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R168">
@@ -60464,7 +60464,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -60534,7 +60534,7 @@
       </c>
       <c r="Q170" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R170">
@@ -60552,7 +60552,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
@@ -60622,7 +60622,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="R171">
@@ -60640,7 +60640,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -60710,7 +60710,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="R172">
@@ -60728,7 +60728,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
@@ -60798,7 +60798,7 @@
       </c>
       <c r="Q173" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R173">
@@ -60816,7 +60816,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -60886,7 +60886,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R174">
@@ -60992,7 +60992,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -61062,7 +61062,7 @@
       </c>
       <c r="Q176" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="R176">
@@ -61080,7 +61080,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -61150,7 +61150,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R177">
@@ -61168,7 +61168,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -61238,7 +61238,7 @@
       </c>
       <c r="Q178" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R178">
@@ -61256,7 +61256,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -61326,7 +61326,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R179">
@@ -61344,7 +61344,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -61414,7 +61414,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R180">
@@ -61432,7 +61432,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -61502,7 +61502,7 @@
       </c>
       <c r="Q181" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="R181">
@@ -61520,7 +61520,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -61590,7 +61590,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R182">
@@ -61608,7 +61608,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -61678,7 +61678,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R183">
@@ -61696,7 +61696,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -61766,7 +61766,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R184">
@@ -61784,7 +61784,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="Q185" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R185">
@@ -61872,7 +61872,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -61942,7 +61942,7 @@
       </c>
       <c r="Q186" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="R186">
@@ -62048,7 +62048,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -62114,7 +62114,7 @@
       </c>
       <c r="Q188" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="R188">
@@ -62132,7 +62132,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -62202,7 +62202,7 @@
       </c>
       <c r="Q189" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="R189">
@@ -62220,7 +62220,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -62290,7 +62290,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R190">
@@ -62308,7 +62308,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
@@ -62378,7 +62378,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R191">
@@ -62396,7 +62396,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -62462,7 +62462,7 @@
       </c>
       <c r="Q192" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R192">
@@ -62480,7 +62480,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -62550,7 +62550,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="R193">
@@ -62568,7 +62568,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -62638,7 +62638,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R194">
@@ -62656,7 +62656,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Trabzon</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -62726,7 +62726,7 @@
       </c>
       <c r="Q195" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Trabzon</t>
         </is>
       </c>
       <c r="R195">
@@ -62744,7 +62744,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -62814,7 +62814,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="R196">
@@ -62920,7 +62920,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -62990,7 +62990,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R198">
@@ -63008,7 +63008,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
@@ -63078,7 +63078,7 @@
       </c>
       <c r="Q199" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Samsun</t>
         </is>
       </c>
       <c r="R199">
@@ -63096,7 +63096,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -63166,7 +63166,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R200">
@@ -63184,7 +63184,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
@@ -63254,7 +63254,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="R201">
@@ -63272,7 +63272,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -63342,7 +63342,7 @@
       </c>
       <c r="Q202" s="6" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="R202">
@@ -63360,7 +63360,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
@@ -63430,7 +63430,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="R203">
@@ -63448,7 +63448,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -63518,7 +63518,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="R204">
@@ -64685,7 +64685,7 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Trabzon</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -68305,7 +68305,7 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>Kütahya</t>
+          <t>Eskişehir</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
@@ -76439,7 +76439,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>100m Serbest</t>
@@ -76468,6 +76467,11 @@
       <c r="L351" t="inlineStr">
         <is>
           <t>28.72</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Kayseri Su Sporları Spor Kulübü</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
@@ -76508,7 +76512,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>100m Serbest</t>
@@ -76537,6 +76540,11 @@
       <c r="L352" t="inlineStr">
         <is>
           <t>1:05.40</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
@@ -76577,7 +76585,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
           <t>100m Kelebek</t>
@@ -76616,6 +76623,11 @@
       <c r="N353" t="inlineStr">
         <is>
           <t>57.28</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Enka Spor Kulübü</t>
         </is>
       </c>
       <c r="Q353" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -59714,7 +59714,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>2:24.85</t>
+          <t>2:18.03</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -60876,7 +60876,7 @@
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
-          <t>3:11.89</t>
+          <t>3:07.35</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -61996,7 +61996,7 @@
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>2:44.64</t>
+          <t>2:40.28</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -62256,7 +62256,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -62276,7 +62276,7 @@
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>1:54.46</t>
+          <t>1:08.78</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -62716,7 +62716,7 @@
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>5:35.19</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -62950,7 +62950,7 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>1:03.10</t>
+          <t>1:02.32</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr">
@@ -62960,7 +62960,7 @@
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
-          <t>1:13.14</t>
+          <t>1:12.45</t>
         </is>
       </c>
       <c r="K198" s="4" t="inlineStr">
@@ -62970,7 +62970,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2:18.60</t>
+          <t>2:16.56</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -62980,7 +62980,7 @@
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
-          <t>2:48.20</t>
+          <t>2:35.67</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -63126,7 +63126,7 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
@@ -63234,7 +63234,7 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>1:10.35</t>
+          <t>1:07.61</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -63302,7 +63302,7 @@
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>1:18.34</t>
+          <t>1:15.64</t>
         </is>
       </c>
       <c r="I202" s="4" t="inlineStr">
@@ -63332,7 +63332,7 @@
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>5:49.65</t>
         </is>
       </c>
       <c r="P202" s="12" t="inlineStr">
@@ -63410,7 +63410,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>4:13.50</t>
+          <t>4:06.09</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
@@ -63498,7 +63498,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>10:58.63</t>
+          <t>10:42.33</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
-          <t>2:50.01</t>
+          <t>2:47.79</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -63576,7 +63576,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>2:42.01</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -63596,7 +63596,7 @@
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>2:50.30</t>
+          <t>2:45.93</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -63654,7 +63654,7 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>19:52.42</t>
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr">
@@ -63684,7 +63684,7 @@
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>6:01.82</t>
         </is>
       </c>
       <c r="P206" s="12" t="inlineStr">
@@ -63742,7 +63742,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>10:37.45</t>
+          <t>9:42.66</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
@@ -63752,7 +63752,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2:53.05</t>
+          <t>2:38.68</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -63762,7 +63762,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>21:34.28</t>
+          <t>18:34.24</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -63772,7 +63772,7 @@
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>5:51.23</t>
+          <t>5:30.64</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -63835,7 +63835,7 @@
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>1:02.12</t>
+          <t>1:00.44</t>
         </is>
       </c>
       <c r="I208" s="4" t="inlineStr">
@@ -63855,7 +63855,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>1:04.67</t>
+          <t>1:03.62</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr">
@@ -63865,7 +63865,7 @@
       </c>
       <c r="N208" s="4" t="inlineStr">
         <is>
-          <t>2:35.32</t>
+          <t>2:26.78</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -63933,7 +63933,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>3:00.11</t>
+          <t>2:36.07</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -63953,7 +63953,7 @@
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>2:55.74</t>
+          <t>2:34.89</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -64207,7 +64207,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>8:46.58</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -64466,7 +64466,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>23:14.93</t>
+          <t>20:10.47</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -64476,7 +64476,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>12:01.37</t>
+          <t>10:27.69</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
@@ -64486,7 +64486,7 @@
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>2:45.97</t>
+          <t>2:39.60</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -64544,7 +64544,7 @@
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="I216" s="4" t="inlineStr">
@@ -64554,7 +64554,7 @@
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
-          <t>1:05.17</t>
+          <t>1:04.61</t>
         </is>
       </c>
       <c r="K216" s="4" t="inlineStr">
@@ -64564,7 +64564,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>1:18.39</t>
+          <t>1:14.50</t>
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr">
@@ -64574,7 +64574,7 @@
       </c>
       <c r="N216" s="4" t="inlineStr">
         <is>
-          <t>2:27.96</t>
+          <t>2:26.64</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -64818,7 +64818,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -65366,7 +65366,7 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>1:17.94</t>
+          <t>1:16.05</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr">
@@ -65376,7 +65376,7 @@
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t>6:23.01</t>
+          <t>6:09.57</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -65434,7 +65434,7 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>11:48.36</t>
+          <t>10:45.92</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
@@ -65444,7 +65444,7 @@
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>2:46.48</t>
+          <t>2:44.17</t>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -65464,7 +65464,7 @@
       </c>
       <c r="N226" s="4" t="inlineStr">
         <is>
-          <t>2:50.65</t>
+          <t>2:49.61</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -65874,7 +65874,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>11:43.65</t>
+          <t>10:29.68</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -65894,7 +65894,7 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>22:49.37</t>
+          <t>20:03.79</t>
         </is>
       </c>
       <c r="M231" s="2" t="inlineStr">
@@ -65904,7 +65904,7 @@
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>5:45.97</t>
         </is>
       </c>
       <c r="P231" s="12" t="inlineStr">
@@ -74178,7 +74178,7 @@
       </c>
       <c r="L325" s="4" t="inlineStr">
         <is>
-          <t>1:15.34</t>
+          <t>1:13.94</t>
         </is>
       </c>
       <c r="M325" s="4" t="inlineStr">
@@ -74188,7 +74188,7 @@
       </c>
       <c r="N325" s="4" t="inlineStr">
         <is>
-          <t>2:49.58</t>
+          <t>2:47.58</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
@@ -74246,7 +74246,7 @@
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>1:04.08</t>
+          <t>1:03.14</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -74256,7 +74256,7 @@
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>1:13.80</t>
+          <t>1:11.62</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -74344,7 +74344,7 @@
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>2:46.50</t>
+          <t>2:41.55</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -74442,7 +74442,7 @@
       </c>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>1:29.53</t>
         </is>
       </c>
       <c r="M328" s="2" t="inlineStr">
@@ -74540,7 +74540,7 @@
       </c>
       <c r="N329" s="4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>5:52.17</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
@@ -74706,7 +74706,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>1:13.51</t>
+          <t>1:12.64</t>
         </is>
       </c>
       <c r="M331" s="4" t="inlineStr">
@@ -74784,7 +74784,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>10:22.10</t>
+          <t>10:12.52</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -62540,7 +62540,7 @@
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -63214,7 +63214,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>31.60</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -64099,7 +64099,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
@@ -64378,7 +64378,7 @@
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t>1:08.66</t>
+          <t>1:08.49</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr">
@@ -65097,7 +65097,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>1:29.67</t>
+          <t>1:27.38</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -74158,7 +74158,7 @@
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>1:08.52</t>
+          <t>1:08.45</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
@@ -74520,7 +74520,7 @@
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>2:43.29</t>
+          <t>2:42.84</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -74804,7 +74804,7 @@
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
-          <t>19:45.31</t>
+          <t>19:45.16</t>
         </is>
       </c>
       <c r="P332" s="6" t="inlineStr">

--- a/SEM_kontrol_liste.xlsx
+++ b/SEM_kontrol_liste.xlsx
@@ -73982,7 +73982,7 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>1:08.31</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
